--- a/02_Шаблоны_и_Форматки/Справочники/ЛЗК_бланки.xlsx
+++ b/02_Шаблоны_и_Форматки/Справочники/ЛЗК_бланки.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Подписи (через «;»)</t>
+          <t>Подписи (через «;»; пусто — без подписей)</t>
         </is>
       </c>
     </row>
@@ -472,11 +472,7 @@
           <t>Раскрой — по DXF (03_ЧПУ\Лазер_Лист) и IGS (03_ЧПУ\Труборез) изделия. Заусенцы удалить, заготовки маркировать обозначением.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Начальник КТО; Начальник участка</t>
-        </is>
-      </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -494,11 +490,7 @@
           <t>Сварка — по чертежам сборочных единиц (02_PDF). Швы зачистить, брызги металла удалить.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Начальник КТО; Начальник участка</t>
-        </is>
-      </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -516,11 +508,7 @@
           <t>Порошковая окраска, цвет — в шапке листа. Перед окраской — обезжиривание.</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Начальник КТО; Начальник участка</t>
-        </is>
-      </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -538,16 +526,12 @@
           <t>Комплектовать по листу. Покупные и стандартные изделия — со склада по коду 1С.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Начальник КТО; Начальник участка</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Положите файл рядом с Нормативы_производства.xlsx (рядом с корнем заказов). Кнопка «Ведомость ЛЗК» берёт отсюда операции участков, указания и подписи; пустая ячейка — значение по умолчанию.</t>
+          <t>Положите файл рядом с Нормативы_производства.xlsx (рядом с корнем заказов). Кнопка «Ведомость ЛЗК» берёт отсюда операции участков и указания; пустая ячейка — значение по умолчанию. Подписи внизу листа участка — только если вписаны в столбец D (по умолчанию их нет, решение владельца 19.09.2026).</t>
         </is>
       </c>
     </row>
